--- a/BED_data.xlsx
+++ b/BED_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msilv\Documents\GitHub\Sunk-entry-costs--endogenous-variety--and-unemployment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AA6709-DD72-4A8A-BD0D-650104EF839E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1666679-AFA1-4004-836C-48675FB416D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BLS Data Series" sheetId="1" r:id="rId1"/>
@@ -31921,7 +31921,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="#0.0"/>
+    <numFmt numFmtId="164" formatCode="#0.0"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -32073,16 +32073,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -32098,17 +32094,21 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -32171,6 +32171,119 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1041">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C371099-AE26-1C81-1C83-B7D79E7805AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6362700"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>234950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5145" name="AutoShape 2073">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BAD3C4A-6C4A-49A5-EB31-BC59D0C0D198}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6362700"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -32506,22 +32619,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
@@ -32532,19 +32645,19 @@
       </c>
     </row>
     <row r="3" spans="1:133" x14ac:dyDescent="0.35">
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="4" spans="1:133" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -36085,15 +36198,15 @@
     </row>
     <row r="13" spans="1:133" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:133" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:133" x14ac:dyDescent="0.35">
-      <c r="E15" s="10"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:133" x14ac:dyDescent="0.35">
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="9" t="s">
         <v>146</v>
       </c>
     </row>
@@ -36126,7 +36239,7 @@
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="13" t="s">
         <v>136</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -39895,7 +40008,8 @@
     <row r="131" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -39904,14 +40018,15 @@
   <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="19.36328125" customWidth="1"/>
     <col min="2" max="2" width="50.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="31" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
         <v>148</v>
       </c>
     </row>
@@ -39922,467 +40037,467 @@
       <c r="B2" s="16"/>
     </row>
     <row r="3" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="12" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="31" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="12" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="12" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="12" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="31" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="12" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="31" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="12" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="17"/>
     </row>
     <row r="15" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B27" s="14"/>
+      <c r="B27" s="17"/>
     </row>
     <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="11" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="11" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="11" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="14"/>
+      <c r="B39" s="17"/>
     </row>
     <row r="40" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="11" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="11" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="11" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="11" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="11" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B51" s="14"/>
+      <c r="B51" s="17"/>
     </row>
     <row r="52" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="11" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="11" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="11" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="11" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B63" s="14"/>
+      <c r="B63" s="17"/>
     </row>
     <row r="64" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="11" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="12" t="s">
+      <c r="A65" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="11" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="11" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="11" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="11" t="s">
         <v>165</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A63:B63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
